--- a/results/block3_results/cad-rads/Synthetic_1/patient_report_Synthetic_1.xlsx
+++ b/results/block3_results/cad-rads/Synthetic_1/patient_report_Synthetic_1.xlsx
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>2.638316389468243</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
